--- a/data/trans_orig/IP07C09-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07C09-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido hablar de todos sus amigos en 2007 (tasa de respuesta: 89,49%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as en 2007 (tasa de respuesta: 89,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13682</t>
+          <t>13206</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23695</t>
+          <t>23758</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12508</t>
+          <t>12685</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21963</t>
+          <t>22404</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28773</t>
+          <t>28707</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43201</t>
+          <t>43028</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,34%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12415</t>
+          <t>12969</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22696</t>
+          <t>23031</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11773</t>
+          <t>11505</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21100</t>
+          <t>21019</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26504</t>
+          <t>27038</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41303</t>
+          <t>40979</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,61%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7909</t>
+          <t>7773</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4237</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2180</t>
+          <t>1724</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9801</t>
+          <t>9293</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8226</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16076</t>
+          <t>16198</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7508</t>
+          <t>7640</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16133</t>
+          <t>15774</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18149</t>
+          <t>17916</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29495</t>
+          <t>30265</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>55,35%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6750</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14872</t>
+          <t>14899</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11034</t>
+          <t>10788</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19705</t>
+          <t>19378</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20520</t>
+          <t>20333</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32465</t>
+          <t>31711</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>58,0%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>675</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5376</t>
+          <t>5343</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>637</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>5770</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2297</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9452</t>
+          <t>9617</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7271</t>
+          <t>7084</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15338</t>
+          <t>15387</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16252</t>
+          <t>16266</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27528</t>
+          <t>27816</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25637</t>
+          <t>26067</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40168</t>
+          <t>40202</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,5%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10042</t>
+          <t>10184</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18544</t>
+          <t>18413</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16308</t>
+          <t>16624</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27563</t>
+          <t>28146</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29390</t>
+          <t>28805</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44257</t>
+          <t>42852</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>54,9%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6419</t>
+          <t>6567</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9092</t>
+          <t>9093</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3964</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12126</t>
+          <t>12369</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4641</t>
+          <t>4454</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4873</t>
+          <t>4639</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31324</t>
+          <t>30042</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46609</t>
+          <t>45701</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31652</t>
+          <t>30784</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46327</t>
+          <t>45623</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>66272</t>
+          <t>66456</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>87193</t>
+          <t>85576</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>51,34%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>31877</t>
+          <t>32663</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>46551</t>
+          <t>48501</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27228</t>
+          <t>27388</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>41433</t>
+          <t>42146</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>63484</t>
+          <t>64801</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>85642</t>
+          <t>83545</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>50,12%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3177</t>
+          <t>3322</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11330</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4609</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13478</t>
+          <t>13990</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9911</t>
+          <t>9719</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22215</t>
+          <t>22172</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3404</t>
+          <t>3361</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3341</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>15925</t>
+          <t>16528</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>27054</t>
+          <t>27471</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>19060</t>
+          <t>18748</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>30923</t>
+          <t>31080</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>37660</t>
+          <t>38085</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>54672</t>
+          <t>55354</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>50,05%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>17022</t>
+          <t>16850</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28326</t>
+          <t>27559</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>24732</t>
+          <t>24803</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>36852</t>
+          <t>36954</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>44313</t>
+          <t>44482</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>62002</t>
+          <t>61606</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>55,71%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>652</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5954</t>
+          <t>6381</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11599</t>
+          <t>11888</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5810</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>15376</t>
+          <t>15380</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,91%</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6045</t>
+          <t>5890</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>14408</t>
+          <t>14702</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9454</t>
+          <t>8913</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>18325</t>
+          <t>18318</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>18063</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>30543</t>
+          <t>30413</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,63%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>20822</t>
+          <t>20448</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>29757</t>
+          <t>29230</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>11063</t>
+          <t>11336</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>19900</t>
+          <t>20362</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>34285</t>
+          <t>34097</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>47187</t>
+          <t>46719</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,02%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>711</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6144</t>
+          <t>6703</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>573</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5115</t>
+          <t>4606</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>9122</t>
+          <t>9007</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3830</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3410</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>99199</t>
+          <t>100007</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>124738</t>
+          <t>125504</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>114164</t>
+          <t>114334</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>141710</t>
+          <t>142071</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>221539</t>
+          <t>222312</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>258585</t>
+          <t>258146</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,53%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>117334</t>
+          <t>116075</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>143062</t>
+          <t>141633</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>120463</t>
+          <t>120430</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>148434</t>
+          <t>148062</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>246044</t>
+          <t>245869</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>282903</t>
+          <t>282892</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>50,99%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>14211</t>
+          <t>14436</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>28204</t>
+          <t>28725</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>18753</t>
+          <t>18987</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>34500</t>
+          <t>34610</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>37813</t>
+          <t>36683</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>58519</t>
+          <t>57691</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>662</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>6708</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>1469</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>8741</t>
+          <t>8541</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido hablar de todos sus amigos en 2012 (tasa de respuesta: 95,1%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as en 2012 (tasa de respuesta: 95,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14603</t>
+          <t>14366</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24586</t>
+          <t>24504</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16228</t>
+          <t>16268</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25536</t>
+          <t>25326</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34181</t>
+          <t>33456</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46914</t>
+          <t>46780</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>67,01%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6575</t>
+          <t>6412</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15322</t>
+          <t>15688</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5924</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14754</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15344</t>
+          <t>15245</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27055</t>
+          <t>26879</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,5%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9173</t>
+          <t>8834</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>621</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5652</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>2790</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11355</t>
+          <t>10956</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6084,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>4071</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3932</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t>4887</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3536</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3614</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15732</t>
+          <t>15255</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24761</t>
+          <t>24180</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15125</t>
+          <t>14902</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24695</t>
+          <t>24559</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33037</t>
+          <t>33165</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46562</t>
+          <t>46251</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,31%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5775</t>
+          <t>5816</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14224</t>
+          <t>14219</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8379</t>
+          <t>8179</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17581</t>
+          <t>17478</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17075</t>
+          <t>16268</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30377</t>
+          <t>29413</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>43,44%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>608</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>4842</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,82 +6663,82 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>14,85%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1297</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>4603</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>13,11%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>3204</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>1248</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>7126</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>1,84%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>16,1%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>1297</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>3995</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>11,38%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>3204</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>1234</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>6643</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>4,73%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3764</t>
+          <t>3237</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3765</t>
+          <t>3542</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4648</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t>3793</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6323</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17009</t>
+          <t>16787</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28190</t>
+          <t>27383</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13523</t>
+          <t>13309</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22072</t>
+          <t>22270</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33520</t>
+          <t>32344</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47381</t>
+          <t>46987</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,18%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10735</t>
+          <t>11275</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21097</t>
+          <t>21779</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6563</t>
+          <t>6260</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15075</t>
+          <t>14399</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20064</t>
+          <t>20395</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33056</t>
+          <t>33405</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,92%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8184</t>
+          <t>8189</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>716</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6586</t>
+          <t>5943</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>3543</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11531</t>
+          <t>11542</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2445</t>
+          <t>3463</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3519</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35941</t>
+          <t>35839</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51023</t>
+          <t>51066</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43837</t>
+          <t>44265</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>60740</t>
+          <t>61026</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>85240</t>
+          <t>83929</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>107090</t>
+          <t>106753</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>59,34%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23510</t>
+          <t>23697</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>38721</t>
+          <t>37816</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24492</t>
+          <t>23392</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>39674</t>
+          <t>39458</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>50805</t>
+          <t>52143</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>73029</t>
+          <t>74175</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>41,23%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5204</t>
+          <t>5140</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14967</t>
+          <t>15273</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4996</t>
+          <t>4686</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13831</t>
+          <t>14743</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>12028</t>
+          <t>12245</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>25119</t>
+          <t>25865</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4390</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3816</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -8243,7 +8243,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4940</t>
+          <t>4431</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4719</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>727</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6981</t>
+          <t>6932</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>28042</t>
+          <t>28535</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>42571</t>
+          <t>43175</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>34649</t>
+          <t>34449</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>48541</t>
+          <t>48305</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>67240</t>
+          <t>66721</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>87004</t>
+          <t>87232</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,46%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>27126</t>
+          <t>27027</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>41833</t>
+          <t>41543</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>19528</t>
+          <t>18776</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32767</t>
+          <t>32105</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>48940</t>
+          <t>50310</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>69431</t>
+          <t>69975</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,7%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>667</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6622</t>
+          <t>6018</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>675</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>7030</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2644</t>
+          <t>2546</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>10258</t>
+          <t>10197</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -8812,7 +8812,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>4639</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4427</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t>4878</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8960,7 +8960,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>724</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7010</t>
+          <t>7655</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6151</t>
+          <t>6499</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>13949</t>
+          <t>14223</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>15349</t>
+          <t>16185</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>25407</t>
+          <t>25711</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>24740</t>
+          <t>24328</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>36954</t>
+          <t>37178</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>64,04%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7675</t>
+          <t>7381</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15666</t>
+          <t>15195</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7916</t>
+          <t>7823</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>17847</t>
+          <t>17142</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>18051</t>
+          <t>18260</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>30480</t>
+          <t>30896</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>53,22%</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>599</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5512</t>
+          <t>5462</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7351</t>
+          <t>6982</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>136842</t>
+          <t>136489</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>164807</t>
+          <t>164339</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>158330</t>
+          <t>159022</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>187329</t>
+          <t>186395</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>303827</t>
+          <t>304139</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>343513</t>
+          <t>342085</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,34%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>99756</t>
+          <t>99128</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>126496</t>
+          <t>126794</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>90161</t>
+          <t>90462</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>118131</t>
+          <t>115558</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>194543</t>
+          <t>197825</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>234846</t>
+          <t>235019</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,4%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>17017</t>
+          <t>16993</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>33146</t>
+          <t>32829</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>13839</t>
+          <t>13672</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>27196</t>
+          <t>27516</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>34893</t>
+          <t>33838</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>54736</t>
+          <t>54656</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>686</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>6412</t>
+          <t>6319</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>6759</t>
+          <t>6842</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>11011</t>
+          <t>10172</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1542</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>9254</t>
+          <t>9775</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>6987</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>4032</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>13864</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido hablar de todos sus amigos en 2016 (tasa de respuesta: 95,28%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as en 2016 (tasa de respuesta: 95,28%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16168</t>
+          <t>16265</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24921</t>
+          <t>25116</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19154</t>
+          <t>19323</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28864</t>
+          <t>29043</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38267</t>
+          <t>38726</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52030</t>
+          <t>52024</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,27%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7096</t>
+          <t>6852</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15821</t>
+          <t>15651</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>4232</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12305</t>
+          <t>12539</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12549</t>
+          <t>12819</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25026</t>
+          <t>25100</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,83%</t>
         </is>
       </c>
     </row>
@@ -10979,7 +10979,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2972</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8777</t>
+          <t>8820</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2346</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9990</t>
+          <t>9492</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -11127,7 +11127,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>3592</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11162,7 +11162,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2757</t>
+          <t>3321</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2277</t>
+          <t>3328</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22583</t>
+          <t>22704</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34201</t>
+          <t>34131</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27067</t>
+          <t>26949</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37647</t>
+          <t>37219</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52676</t>
+          <t>52729</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68495</t>
+          <t>68719</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,86%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9610</t>
+          <t>9794</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19604</t>
+          <t>19971</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7810</t>
+          <t>8058</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18354</t>
+          <t>17649</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19204</t>
+          <t>20036</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33927</t>
+          <t>34588</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,67%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2534</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10186</t>
+          <t>10207</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>718</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>6893</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4735</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13728</t>
+          <t>13423</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -11774,7 +11774,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4404</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11705</t>
+          <t>12202</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20387</t>
+          <t>20632</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17916</t>
+          <t>18076</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27628</t>
+          <t>28369</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32691</t>
+          <t>31951</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46279</t>
+          <t>46298</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,64%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4550</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12687</t>
+          <t>12393</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>9581</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19995</t>
+          <t>19453</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16816</t>
+          <t>16617</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>29837</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,23%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>610</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5765</t>
+          <t>6419</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>704</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5729</t>
+          <t>5535</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1759</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8928</t>
+          <t>9327</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -12456,7 +12456,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2840</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>3150</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>58747</t>
+          <t>59036</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>75787</t>
+          <t>75593</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46682</t>
+          <t>47161</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>63018</t>
+          <t>63834</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>110746</t>
+          <t>111450</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>135583</t>
+          <t>135222</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,74%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>25801</t>
+          <t>25532</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>41039</t>
+          <t>41623</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>23506</t>
+          <t>23079</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>38750</t>
+          <t>39986</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>52206</t>
+          <t>53572</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>75485</t>
+          <t>75028</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>35,92%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4719</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14087</t>
+          <t>14458</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5137</t>
+          <t>4943</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15249</t>
+          <t>14644</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11713</t>
+          <t>11476</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>25805</t>
+          <t>25297</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,11%</t>
         </is>
       </c>
     </row>
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13153,77 +13153,77 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1476</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5058</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>5,19%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>2268</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>6045</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>2,89%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1476</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>5160</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>2268</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>6070</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4722</t>
+          <t>4888</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3508</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>626</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5809</t>
+          <t>6049</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>33778</t>
+          <t>33504</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>47994</t>
+          <t>47522</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>29546</t>
+          <t>29587</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>43802</t>
+          <t>43966</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>67350</t>
+          <t>67607</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>87476</t>
+          <t>87191</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,27%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>18808</t>
+          <t>19295</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>32682</t>
+          <t>33199</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>18321</t>
+          <t>18371</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32110</t>
+          <t>31684</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>41196</t>
+          <t>41112</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>59690</t>
+          <t>59863</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>42,07%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>2375</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10687</t>
+          <t>10433</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2415</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9944</t>
+          <t>10225</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6335</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>16779</t>
+          <t>17685</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,43%</t>
         </is>
       </c>
     </row>
@@ -13820,7 +13820,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>3907</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13835,7 +13835,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13855,7 +13855,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5069</t>
+          <t>5668</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -13933,7 +13933,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2602</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13948,7 +13948,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13968,7 +13968,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3951</t>
+          <t>3902</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>609</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5651</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>13802</t>
+          <t>13746</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>23348</t>
+          <t>23156</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>18888</t>
+          <t>19086</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>28557</t>
+          <t>28626</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>35066</t>
+          <t>35619</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>48867</t>
+          <t>49015</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,51%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4484</t>
+          <t>4299</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13502</t>
+          <t>12931</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>5619</t>
+          <t>5730</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>14495</t>
+          <t>14494</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,7 +14321,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>12176</t>
+          <t>11883</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>24828</t>
+          <t>23997</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>34,03%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>10194</t>
+          <t>10226</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>709</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6398</t>
+          <t>6492</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4819</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>14041</t>
+          <t>14192</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -14502,7 +14502,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14517,7 +14517,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14537,7 +14537,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14552,7 +14552,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14572,7 +14572,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>179559</t>
+          <t>177046</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>209010</t>
+          <t>206011</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,47 +14855,47 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
+          <t>54,08%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>62,92%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>196103</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>180291</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>209748</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>59,65%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
           <t>54,84%</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>63,84%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>196103</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>179916</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>209120</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>59,65%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>54,73%</t>
-        </is>
-      </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>369907</t>
+          <t>365159</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>410991</t>
+          <t>409833</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,46%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>86551</t>
+          <t>87871</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>113860</t>
+          <t>115013</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>87001</t>
+          <t>87057</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>114912</t>
+          <t>115155</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>180365</t>
+          <t>182447</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>219955</t>
+          <t>222145</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,86%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>20221</t>
+          <t>19969</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>37102</t>
+          <t>36273</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>18641</t>
+          <t>18759</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>35850</t>
+          <t>35297</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>44107</t>
+          <t>43322</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>67112</t>
+          <t>67740</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>7778</t>
+          <t>7715</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15199,7 +15199,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>8414</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>3634</t>
+          <t>3723</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>13455</t>
+          <t>12960</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5740</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,47 +15307,47 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>6109</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>2490</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>638</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>5725</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>9157</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
